--- a/Unity/Assets/Config/Excel/Datas/ActionEventConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/ActionEventConfig.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="22080" windowHeight="12180"/>
   </bookViews>
   <sheets>
-    <sheet name="Buff" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="#说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>##var</t>
   </si>
@@ -45,7 +45,7 @@
     <t>ActionEventType</t>
   </si>
   <si>
-    <t>TestType</t>
+    <t>IsClientOnly</t>
   </si>
   <si>
     <t>Params</t>
@@ -63,6 +63,9 @@
     <t>EActionEventType</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>(list#sep=,),int</t>
   </si>
   <si>
@@ -81,10 +84,10 @@
     <t>事件类型</t>
   </si>
   <si>
-    <t>测试类型</t>
-  </si>
-  <si>
-    <t>标签</t>
+    <t>客户端独有</t>
+  </si>
+  <si>
+    <t>参数</t>
   </si>
   <si>
     <t>normal bullet</t>
@@ -109,7 +112,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,11 +154,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -309,7 +307,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -639,136 +637,136 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -790,12 +788,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1152,7 +1144,7 @@
   <cols>
     <col min="1" max="1" width="11.5" style="7" customWidth="1"/>
     <col min="2" max="2" width="9" style="7"/>
-    <col min="3" max="3" width="17.625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="14.875" style="7" customWidth="1"/>
     <col min="4" max="4" width="23.5" style="7" customWidth="1"/>
     <col min="5" max="5" width="18.75" style="7" customWidth="1"/>
     <col min="6" max="6" width="13.75" style="7" customWidth="1"/>
@@ -1201,70 +1193,74 @@
         <v>10</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="16.5" spans="1:7">
       <c r="A3" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="16.5" spans="2:7">
-      <c r="B4" s="9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="13.5" spans="2:7">
+      <c r="B4" s="2">
         <v>1</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="D4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="9">
-        <v>1</v>
-      </c>
-      <c r="G4" s="9"/>
-    </row>
-    <row r="5" s="2" customFormat="1" ht="16.5" spans="2:7">
-      <c r="B5" s="9">
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="13.5" spans="2:7">
+      <c r="B5" s="2">
         <v>2</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="C5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="9">
-        <v>2</v>
-      </c>
-      <c r="G5" s="9"/>
+      <c r="D5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>5001</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/Datas/ActionEventConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/ActionEventConfig.xlsx
@@ -72,7 +72,7 @@
     <t>##</t>
   </si>
   <si>
-    <t>buffID</t>
+    <t>行为事件ID</t>
   </si>
   <si>
     <t>名称</t>
@@ -1143,7 +1143,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.5" style="7" customWidth="1"/>
-    <col min="2" max="2" width="9" style="7"/>
+    <col min="2" max="2" width="10.875" style="7" customWidth="1"/>
     <col min="3" max="3" width="14.875" style="7" customWidth="1"/>
     <col min="4" max="4" width="23.5" style="7" customWidth="1"/>
     <col min="5" max="5" width="18.75" style="7" customWidth="1"/>

--- a/Unity/Assets/Config/Excel/Datas/ActionEventConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/ActionEventConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="#说明" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -48,7 +48,7 @@
     <t>IsClientOnly</t>
   </si>
   <si>
-    <t>Params</t>
+    <t>EventData</t>
   </si>
   <si>
     <t>##type</t>
@@ -66,7 +66,7 @@
     <t>bool</t>
   </si>
   <si>
-    <t>(list#sep=,),int</t>
+    <t>ActionEventBaseData</t>
   </si>
   <si>
     <t>##</t>
@@ -87,19 +87,91 @@
     <t>客户端独有</t>
   </si>
   <si>
-    <t>参数</t>
-  </si>
-  <si>
-    <t>normal bullet</t>
-  </si>
-  <si>
-    <t>emit a bullet</t>
+    <t>????</t>
+  </si>
+  <si>
+    <t>range_damage</t>
+  </si>
+  <si>
+    <t>range damage around owner</t>
   </si>
   <si>
     <t>RangeDamage</t>
   </si>
   <si>
+    <t>range,2000</t>
+  </si>
+  <si>
+    <t>basic_bullet</t>
+  </si>
+  <si>
+    <t>single projectile without on-hit events</t>
+  </si>
+  <si>
     <t>Bullet</t>
+  </si>
+  <si>
+    <t>bullet,5001,10000,1000,200,1,0</t>
+  </si>
+  <si>
+    <t>bullet_hit_damage</t>
+  </si>
+  <si>
+    <t>projectile hit damage</t>
+  </si>
+  <si>
+    <t>ChangeNumeric</t>
+  </si>
+  <si>
+    <t>changenumeric,1001,-15,3,1</t>
+  </si>
+  <si>
+    <t>bullet_hit_mark</t>
+  </si>
+  <si>
+    <t>apply mark buff on hit</t>
+  </si>
+  <si>
+    <t>AddBuff</t>
+  </si>
+  <si>
+    <t>addbuff,8001,3</t>
+  </si>
+  <si>
+    <t>projectile_damage_and_mark_x1</t>
+  </si>
+  <si>
+    <t>1 projectile with on-hit damage and mark</t>
+  </si>
+  <si>
+    <t>bullet,5001,12000,1200,350,1,0,3|4</t>
+  </si>
+  <si>
+    <t>projectile_damage_and_mark_x2</t>
+  </si>
+  <si>
+    <t>2 projectiles with on-hit damage and mark</t>
+  </si>
+  <si>
+    <t>bullet,5001,12000,1200,350,2,8,3|4</t>
+  </si>
+  <si>
+    <t>projectile_damage_and_mark_x3</t>
+  </si>
+  <si>
+    <t>3 projectiles with on-hit damage and mark</t>
+  </si>
+  <si>
+    <t>bullet,5001,12000,1200,350,3,18,3|4</t>
+  </si>
+  <si>
+    <t>projectile_damage_and_mark_x4</t>
+  </si>
+  <si>
+    <t>4 projectiles with on-hit damage and mark</t>
+  </si>
+  <si>
+    <t>bullet,5001,12000,1200,350,4,30,3|4</t>
   </si>
 </sst>
 </file>
@@ -622,172 +694,172 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+  <cellXfs count="50">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1137,23 +1209,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" ns1:Ignorable="xr">
   <sheetPr/>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="11.5" style="7" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="14.875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="23.5" style="7" customWidth="1"/>
-    <col min="5" max="5" width="18.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13.75" style="7" customWidth="1"/>
-    <col min="7" max="7" width="15" style="7" customWidth="1"/>
-    <col min="8" max="8" width="18.875" style="7" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="11.5" customWidth="1" style="7"/>
+    <col min="2" max="2" width="10.875" customWidth="1" style="7"/>
+    <col min="3" max="3" width="14.875" customWidth="1" style="7"/>
+    <col min="4" max="4" width="23.5" customWidth="1" style="7"/>
+    <col min="5" max="5" width="18.75" customWidth="1" style="7"/>
+    <col min="6" max="6" width="13.75" customWidth="1" style="7"/>
+    <col min="7" max="7" width="15" customWidth="1" style="7"/>
+    <col min="8" max="8" width="18.875" customWidth="1" style="7"/>
+    <col min="9" max="16384" width="9" customWidth="1" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" ht="16.5" spans="1:7">
+    <row r="1" ht="16.5" s="2" customFormat="1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1172,11 +1244,13 @@
       <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="16.5" spans="1:7">
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>EventData</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16.5" s="2" customFormat="1">
       <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
@@ -1195,11 +1269,13 @@
       <c r="F2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="16.5" spans="1:7">
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>ActionEventBaseData</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16.5" s="2" customFormat="1">
       <c r="A3" s="8" t="s">
         <v>13</v>
       </c>
@@ -1218,11 +1294,13 @@
       <c r="F3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="13.5" spans="2:7">
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>EventData polymorphic bean range</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="13.5" s="2" customFormat="1">
       <c r="B4" s="2">
         <v>1</v>
       </c>
@@ -1238,31 +1316,377 @@
       <c r="F4" s="2">
         <v>0</v>
       </c>
-      <c r="G4" s="2">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" ht="13.5" spans="2:7">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="13.5" s="2" customFormat="1">
       <c r="B5" s="2">
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
       </c>
-      <c r="G5" s="2">
-        <v>5001</v>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="7">
+        <v>3</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="7">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>changenumeric</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="7">
+        <v>4</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>addbuff</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7">
+        <v>5</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3|4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="7">
+        <v>6</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="7">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3|4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7">
+        <v>7</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3|4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="7">
+        <v>8</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>3|4</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="G1:N1"/>
+    <mergeCell ref="G2:N2"/>
+    <mergeCell ref="G3:N3"/>
+  </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1270,7 +1694,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <sheetPr/>
   <dimension ref="B3:M34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
@@ -1280,7 +1704,7 @@
     <col min="6" max="6" width="18.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="6:13">
+    <row r="3">
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -1290,7 +1714,7 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="6:13">
+    <row r="4">
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -1300,7 +1724,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="6:13">
+    <row r="5">
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -1310,7 +1734,7 @@
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
-    <row r="6" spans="6:13">
+    <row r="6">
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -1320,7 +1744,7 @@
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="6:13">
+    <row r="7">
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -1330,7 +1754,7 @@
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
     </row>
-    <row r="8" spans="6:13">
+    <row r="8">
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -1340,7 +1764,7 @@
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
-    <row r="9" spans="6:13">
+    <row r="9">
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -1350,7 +1774,7 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
     </row>
-    <row r="10" spans="6:13">
+    <row r="10">
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -1360,7 +1784,7 @@
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
-    <row r="11" spans="6:13">
+    <row r="11">
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -1370,7 +1794,7 @@
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
     </row>
-    <row r="12" spans="6:13">
+    <row r="12">
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -1380,7 +1804,7 @@
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
     </row>
-    <row r="13" spans="6:13">
+    <row r="13">
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -1390,7 +1814,7 @@
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" spans="6:13">
+    <row r="14">
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -1400,7 +1824,7 @@
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
     </row>
-    <row r="15" spans="6:13">
+    <row r="15">
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -1410,7 +1834,7 @@
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
     </row>
-    <row r="16" spans="6:13">
+    <row r="16">
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -1420,7 +1844,7 @@
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
     </row>
-    <row r="17" spans="6:13">
+    <row r="17">
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -1430,7 +1854,7 @@
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
     </row>
-    <row r="18" spans="6:13">
+    <row r="18">
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -1440,7 +1864,7 @@
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
     </row>
-    <row r="19" spans="6:13">
+    <row r="19">
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -1450,7 +1874,7 @@
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
     </row>
-    <row r="20" spans="6:13">
+    <row r="20">
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -1460,7 +1884,7 @@
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
     </row>
-    <row r="21" spans="6:13">
+    <row r="21">
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -1470,7 +1894,7 @@
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
     </row>
-    <row r="22" spans="6:13">
+    <row r="22">
       <c r="F22" s="3"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -1480,7 +1904,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
     </row>
-    <row r="23" spans="6:13">
+    <row r="23">
       <c r="F23" s="3"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -1490,7 +1914,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
     </row>
-    <row r="24" spans="6:13">
+    <row r="24">
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -1500,7 +1924,7 @@
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
     </row>
-    <row r="25" spans="6:13">
+    <row r="25">
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -1510,7 +1934,7 @@
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
     </row>
-    <row r="26" spans="6:13">
+    <row r="26">
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -1520,7 +1944,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
     </row>
-    <row r="27" spans="6:13">
+    <row r="27">
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -1530,7 +1954,7 @@
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28">
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -1544,7 +1968,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29">
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -1558,7 +1982,7 @@
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30">
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
@@ -1572,7 +1996,7 @@
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31">
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
@@ -1586,7 +2010,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32">
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -1600,7 +2024,7 @@
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
     </row>
-    <row r="33" spans="2:13">
+    <row r="33">
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -1614,7 +2038,7 @@
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" spans="2:13">
+    <row r="34">
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
